--- a/1.xlsx
+++ b/1.xlsx
@@ -5,10 +5,11 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Лист2" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -1432,4 +1433,83 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="7.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="8.56"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:G52"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;KffffffСтраница &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/1.xlsx
+++ b/1.xlsx
@@ -350,7 +350,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -497,6 +497,10 @@
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1440,66 +1444,423 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="B2:G52"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="7.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="8.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="15" width="5.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="15.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="15" width="7.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="8.56"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="37"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="37"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="37"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="37"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="37"/>
+      <c r="C7" s="37"/>
+      <c r="D7" s="37"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="37"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="37"/>
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="37"/>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="37"/>
+      <c r="C10" s="37"/>
+      <c r="D10" s="37"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="37"/>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="37"/>
+      <c r="C11" s="37"/>
+      <c r="D11" s="37"/>
+      <c r="E11" s="37"/>
+      <c r="F11" s="37"/>
+      <c r="G11" s="37"/>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="37"/>
+      <c r="C12" s="37"/>
+      <c r="D12" s="37"/>
+      <c r="E12" s="37"/>
+      <c r="F12" s="37"/>
+      <c r="G12" s="37"/>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="37"/>
+      <c r="C13" s="37"/>
+      <c r="D13" s="37"/>
+      <c r="E13" s="37"/>
+      <c r="F13" s="37"/>
+      <c r="G13" s="37"/>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="37"/>
+      <c r="C14" s="37"/>
+      <c r="D14" s="37"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="37"/>
+      <c r="G14" s="37"/>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="37"/>
+      <c r="C15" s="37"/>
+      <c r="D15" s="37"/>
+      <c r="E15" s="37"/>
+      <c r="F15" s="37"/>
+      <c r="G15" s="37"/>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="37"/>
+      <c r="C16" s="37"/>
+      <c r="D16" s="37"/>
+      <c r="E16" s="37"/>
+      <c r="F16" s="37"/>
+      <c r="G16" s="37"/>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="37"/>
+      <c r="C17" s="37"/>
+      <c r="D17" s="37"/>
+      <c r="E17" s="37"/>
+      <c r="F17" s="37"/>
+      <c r="G17" s="37"/>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="37"/>
+      <c r="C18" s="37"/>
+      <c r="D18" s="37"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="37"/>
+      <c r="G18" s="37"/>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="37"/>
+      <c r="C19" s="37"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="37"/>
+      <c r="G19" s="37"/>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="37"/>
+      <c r="C20" s="37"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="37"/>
+      <c r="F20" s="37"/>
+      <c r="G20" s="37"/>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="37"/>
+      <c r="C21" s="37"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="37"/>
+      <c r="G21" s="37"/>
+    </row>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="37"/>
+      <c r="C22" s="37"/>
+      <c r="D22" s="37"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="37"/>
+      <c r="G22" s="37"/>
+    </row>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="37"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="37"/>
+      <c r="G23" s="37"/>
+    </row>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="37"/>
+      <c r="C24" s="37"/>
+      <c r="D24" s="37"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="37"/>
+      <c r="G24" s="37"/>
+    </row>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="37"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="37"/>
+      <c r="G25" s="37"/>
+    </row>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="37"/>
+      <c r="C26" s="37"/>
+      <c r="D26" s="37"/>
+      <c r="E26" s="37"/>
+      <c r="F26" s="37"/>
+      <c r="G26" s="37"/>
+    </row>
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="37"/>
+      <c r="C27" s="37"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="37"/>
+      <c r="F27" s="37"/>
+      <c r="G27" s="37"/>
+    </row>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="37"/>
+      <c r="C28" s="37"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="37"/>
+      <c r="G28" s="37"/>
+    </row>
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="37"/>
+      <c r="C29" s="37"/>
+      <c r="D29" s="37"/>
+      <c r="E29" s="37"/>
+      <c r="F29" s="37"/>
+      <c r="G29" s="37"/>
+    </row>
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="37"/>
+      <c r="C30" s="37"/>
+      <c r="D30" s="37"/>
+      <c r="E30" s="37"/>
+      <c r="F30" s="37"/>
+      <c r="G30" s="37"/>
+    </row>
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="37"/>
+      <c r="C31" s="37"/>
+      <c r="D31" s="37"/>
+      <c r="E31" s="37"/>
+      <c r="F31" s="37"/>
+      <c r="G31" s="37"/>
+    </row>
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="37"/>
+      <c r="C32" s="37"/>
+      <c r="D32" s="37"/>
+      <c r="E32" s="37"/>
+      <c r="F32" s="37"/>
+      <c r="G32" s="37"/>
+    </row>
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="37"/>
+      <c r="C33" s="37"/>
+      <c r="D33" s="37"/>
+      <c r="E33" s="37"/>
+      <c r="F33" s="37"/>
+      <c r="G33" s="37"/>
+    </row>
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="37"/>
+      <c r="C34" s="37"/>
+      <c r="D34" s="37"/>
+      <c r="E34" s="37"/>
+      <c r="F34" s="37"/>
+      <c r="G34" s="37"/>
+    </row>
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="37"/>
+      <c r="C35" s="37"/>
+      <c r="D35" s="37"/>
+      <c r="E35" s="37"/>
+      <c r="F35" s="37"/>
+      <c r="G35" s="37"/>
+    </row>
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="37"/>
+      <c r="C36" s="37"/>
+      <c r="D36" s="37"/>
+      <c r="E36" s="37"/>
+      <c r="F36" s="37"/>
+      <c r="G36" s="37"/>
+    </row>
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="37"/>
+      <c r="C37" s="37"/>
+      <c r="D37" s="37"/>
+      <c r="E37" s="37"/>
+      <c r="F37" s="37"/>
+      <c r="G37" s="37"/>
+    </row>
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="37"/>
+      <c r="C38" s="37"/>
+      <c r="D38" s="37"/>
+      <c r="E38" s="37"/>
+      <c r="F38" s="37"/>
+      <c r="G38" s="37"/>
+    </row>
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="37"/>
+      <c r="C39" s="37"/>
+      <c r="D39" s="37"/>
+      <c r="E39" s="37"/>
+      <c r="F39" s="37"/>
+      <c r="G39" s="37"/>
+    </row>
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="37"/>
+      <c r="C40" s="37"/>
+      <c r="D40" s="37"/>
+      <c r="E40" s="37"/>
+      <c r="F40" s="37"/>
+      <c r="G40" s="37"/>
+    </row>
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="37"/>
+      <c r="C41" s="37"/>
+      <c r="D41" s="37"/>
+      <c r="E41" s="37"/>
+      <c r="F41" s="37"/>
+      <c r="G41" s="37"/>
+    </row>
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="37"/>
+      <c r="C42" s="37"/>
+      <c r="D42" s="37"/>
+      <c r="E42" s="37"/>
+      <c r="F42" s="37"/>
+      <c r="G42" s="37"/>
+    </row>
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="37"/>
+      <c r="C43" s="37"/>
+      <c r="D43" s="37"/>
+      <c r="E43" s="37"/>
+      <c r="F43" s="37"/>
+      <c r="G43" s="37"/>
+    </row>
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="37"/>
+      <c r="C44" s="37"/>
+      <c r="D44" s="37"/>
+      <c r="E44" s="37"/>
+      <c r="F44" s="37"/>
+      <c r="G44" s="37"/>
+    </row>
+    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="37"/>
+      <c r="C45" s="37"/>
+      <c r="D45" s="37"/>
+      <c r="E45" s="37"/>
+      <c r="F45" s="37"/>
+      <c r="G45" s="37"/>
+    </row>
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="37"/>
+      <c r="C46" s="37"/>
+      <c r="D46" s="37"/>
+      <c r="E46" s="37"/>
+      <c r="F46" s="37"/>
+      <c r="G46" s="37"/>
+    </row>
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="37"/>
+      <c r="C47" s="37"/>
+      <c r="D47" s="37"/>
+      <c r="E47" s="37"/>
+      <c r="F47" s="37"/>
+      <c r="G47" s="37"/>
+    </row>
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="37"/>
+      <c r="C48" s="37"/>
+      <c r="D48" s="37"/>
+      <c r="E48" s="37"/>
+      <c r="F48" s="37"/>
+      <c r="G48" s="37"/>
+    </row>
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="37"/>
+      <c r="C49" s="37"/>
+      <c r="D49" s="37"/>
+      <c r="E49" s="37"/>
+      <c r="F49" s="37"/>
+      <c r="G49" s="37"/>
+    </row>
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="37"/>
+      <c r="C50" s="37"/>
+      <c r="D50" s="37"/>
+      <c r="E50" s="37"/>
+      <c r="F50" s="37"/>
+      <c r="G50" s="37"/>
+    </row>
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B51" s="37"/>
+      <c r="C51" s="37"/>
+      <c r="D51" s="37"/>
+      <c r="E51" s="37"/>
+      <c r="F51" s="37"/>
+      <c r="G51" s="37"/>
+    </row>
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="37"/>
+      <c r="C52" s="37"/>
+      <c r="D52" s="37"/>
+      <c r="E52" s="37"/>
+      <c r="F52" s="37"/>
+      <c r="G52" s="37"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:G52"/>

--- a/1.xlsx
+++ b/1.xlsx
@@ -5,11 +5,10 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Лист2" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -350,7 +349,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="37">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -497,10 +496,6 @@
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1437,440 +1432,4 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="B2:G52"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="15" width="5.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="15.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="15" width="7.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="8.56"/>
-  </cols>
-  <sheetData>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="37"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="37"/>
-    </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="37"/>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="37"/>
-      <c r="C6" s="37"/>
-      <c r="D6" s="37"/>
-      <c r="E6" s="37"/>
-      <c r="F6" s="37"/>
-      <c r="G6" s="37"/>
-    </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="37"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-    </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="37"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-    </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="37"/>
-      <c r="C9" s="37"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="37"/>
-      <c r="G9" s="37"/>
-    </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="37"/>
-      <c r="C10" s="37"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="37"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="37"/>
-    </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="37"/>
-      <c r="C11" s="37"/>
-      <c r="D11" s="37"/>
-      <c r="E11" s="37"/>
-      <c r="F11" s="37"/>
-      <c r="G11" s="37"/>
-    </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="37"/>
-      <c r="C12" s="37"/>
-      <c r="D12" s="37"/>
-      <c r="E12" s="37"/>
-      <c r="F12" s="37"/>
-      <c r="G12" s="37"/>
-    </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="37"/>
-      <c r="C13" s="37"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="37"/>
-      <c r="G13" s="37"/>
-    </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="37"/>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="37"/>
-      <c r="G14" s="37"/>
-    </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="37"/>
-      <c r="C15" s="37"/>
-      <c r="D15" s="37"/>
-      <c r="E15" s="37"/>
-      <c r="F15" s="37"/>
-      <c r="G15" s="37"/>
-    </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="37"/>
-      <c r="C16" s="37"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="37"/>
-      <c r="G16" s="37"/>
-    </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="37"/>
-      <c r="C17" s="37"/>
-      <c r="D17" s="37"/>
-      <c r="E17" s="37"/>
-      <c r="F17" s="37"/>
-      <c r="G17" s="37"/>
-    </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="37"/>
-      <c r="C18" s="37"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="37"/>
-    </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="37"/>
-      <c r="C19" s="37"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="37"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="37"/>
-    </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="37"/>
-      <c r="C20" s="37"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="37"/>
-      <c r="F20" s="37"/>
-      <c r="G20" s="37"/>
-    </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="37"/>
-      <c r="C21" s="37"/>
-      <c r="D21" s="37"/>
-      <c r="E21" s="37"/>
-      <c r="F21" s="37"/>
-      <c r="G21" s="37"/>
-    </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="37"/>
-      <c r="C22" s="37"/>
-      <c r="D22" s="37"/>
-      <c r="E22" s="37"/>
-      <c r="F22" s="37"/>
-      <c r="G22" s="37"/>
-    </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="37"/>
-      <c r="C23" s="37"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="37"/>
-      <c r="G23" s="37"/>
-    </row>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="37"/>
-      <c r="C24" s="37"/>
-      <c r="D24" s="37"/>
-      <c r="E24" s="37"/>
-      <c r="F24" s="37"/>
-      <c r="G24" s="37"/>
-    </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="37"/>
-      <c r="C25" s="37"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="37"/>
-      <c r="F25" s="37"/>
-      <c r="G25" s="37"/>
-    </row>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="37"/>
-      <c r="C26" s="37"/>
-      <c r="D26" s="37"/>
-      <c r="E26" s="37"/>
-      <c r="F26" s="37"/>
-      <c r="G26" s="37"/>
-    </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="37"/>
-      <c r="C27" s="37"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="37"/>
-      <c r="F27" s="37"/>
-      <c r="G27" s="37"/>
-    </row>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="37"/>
-      <c r="C28" s="37"/>
-      <c r="D28" s="37"/>
-      <c r="E28" s="37"/>
-      <c r="F28" s="37"/>
-      <c r="G28" s="37"/>
-    </row>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="37"/>
-      <c r="C29" s="37"/>
-      <c r="D29" s="37"/>
-      <c r="E29" s="37"/>
-      <c r="F29" s="37"/>
-      <c r="G29" s="37"/>
-    </row>
-    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="37"/>
-      <c r="C30" s="37"/>
-      <c r="D30" s="37"/>
-      <c r="E30" s="37"/>
-      <c r="F30" s="37"/>
-      <c r="G30" s="37"/>
-    </row>
-    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="37"/>
-      <c r="C31" s="37"/>
-      <c r="D31" s="37"/>
-      <c r="E31" s="37"/>
-      <c r="F31" s="37"/>
-      <c r="G31" s="37"/>
-    </row>
-    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="37"/>
-      <c r="C32" s="37"/>
-      <c r="D32" s="37"/>
-      <c r="E32" s="37"/>
-      <c r="F32" s="37"/>
-      <c r="G32" s="37"/>
-    </row>
-    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="37"/>
-      <c r="C33" s="37"/>
-      <c r="D33" s="37"/>
-      <c r="E33" s="37"/>
-      <c r="F33" s="37"/>
-      <c r="G33" s="37"/>
-    </row>
-    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="37"/>
-      <c r="C34" s="37"/>
-      <c r="D34" s="37"/>
-      <c r="E34" s="37"/>
-      <c r="F34" s="37"/>
-      <c r="G34" s="37"/>
-    </row>
-    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="37"/>
-      <c r="C35" s="37"/>
-      <c r="D35" s="37"/>
-      <c r="E35" s="37"/>
-      <c r="F35" s="37"/>
-      <c r="G35" s="37"/>
-    </row>
-    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="37"/>
-      <c r="C36" s="37"/>
-      <c r="D36" s="37"/>
-      <c r="E36" s="37"/>
-      <c r="F36" s="37"/>
-      <c r="G36" s="37"/>
-    </row>
-    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="37"/>
-      <c r="C37" s="37"/>
-      <c r="D37" s="37"/>
-      <c r="E37" s="37"/>
-      <c r="F37" s="37"/>
-      <c r="G37" s="37"/>
-    </row>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="37"/>
-      <c r="C38" s="37"/>
-      <c r="D38" s="37"/>
-      <c r="E38" s="37"/>
-      <c r="F38" s="37"/>
-      <c r="G38" s="37"/>
-    </row>
-    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="37"/>
-      <c r="C39" s="37"/>
-      <c r="D39" s="37"/>
-      <c r="E39" s="37"/>
-      <c r="F39" s="37"/>
-      <c r="G39" s="37"/>
-    </row>
-    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="37"/>
-      <c r="C40" s="37"/>
-      <c r="D40" s="37"/>
-      <c r="E40" s="37"/>
-      <c r="F40" s="37"/>
-      <c r="G40" s="37"/>
-    </row>
-    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="37"/>
-      <c r="C41" s="37"/>
-      <c r="D41" s="37"/>
-      <c r="E41" s="37"/>
-      <c r="F41" s="37"/>
-      <c r="G41" s="37"/>
-    </row>
-    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="37"/>
-      <c r="C42" s="37"/>
-      <c r="D42" s="37"/>
-      <c r="E42" s="37"/>
-      <c r="F42" s="37"/>
-      <c r="G42" s="37"/>
-    </row>
-    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="37"/>
-      <c r="C43" s="37"/>
-      <c r="D43" s="37"/>
-      <c r="E43" s="37"/>
-      <c r="F43" s="37"/>
-      <c r="G43" s="37"/>
-    </row>
-    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="37"/>
-      <c r="C44" s="37"/>
-      <c r="D44" s="37"/>
-      <c r="E44" s="37"/>
-      <c r="F44" s="37"/>
-      <c r="G44" s="37"/>
-    </row>
-    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="37"/>
-      <c r="C45" s="37"/>
-      <c r="D45" s="37"/>
-      <c r="E45" s="37"/>
-      <c r="F45" s="37"/>
-      <c r="G45" s="37"/>
-    </row>
-    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="37"/>
-      <c r="C46" s="37"/>
-      <c r="D46" s="37"/>
-      <c r="E46" s="37"/>
-      <c r="F46" s="37"/>
-      <c r="G46" s="37"/>
-    </row>
-    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="37"/>
-      <c r="C47" s="37"/>
-      <c r="D47" s="37"/>
-      <c r="E47" s="37"/>
-      <c r="F47" s="37"/>
-      <c r="G47" s="37"/>
-    </row>
-    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="37"/>
-      <c r="C48" s="37"/>
-      <c r="D48" s="37"/>
-      <c r="E48" s="37"/>
-      <c r="F48" s="37"/>
-      <c r="G48" s="37"/>
-    </row>
-    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="37"/>
-      <c r="C49" s="37"/>
-      <c r="D49" s="37"/>
-      <c r="E49" s="37"/>
-      <c r="F49" s="37"/>
-      <c r="G49" s="37"/>
-    </row>
-    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="37"/>
-      <c r="C50" s="37"/>
-      <c r="D50" s="37"/>
-      <c r="E50" s="37"/>
-      <c r="F50" s="37"/>
-      <c r="G50" s="37"/>
-    </row>
-    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="37"/>
-      <c r="C51" s="37"/>
-      <c r="D51" s="37"/>
-      <c r="E51" s="37"/>
-      <c r="F51" s="37"/>
-      <c r="G51" s="37"/>
-    </row>
-    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B52" s="37"/>
-      <c r="C52" s="37"/>
-      <c r="D52" s="37"/>
-      <c r="E52" s="37"/>
-      <c r="F52" s="37"/>
-      <c r="G52" s="37"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:G52"/>
-  </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;KffffffСтраница &amp;P</oddFooter>
-  </headerFooter>
-</worksheet>
 </file>
--- a/1.xlsx
+++ b/1.xlsx
@@ -5,10 +5,11 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Лист2" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="51">
   <si>
     <t xml:space="preserve">МАРШРУТНЫЙ ЛИСТ</t>
   </si>
@@ -170,6 +171,9 @@
   </si>
   <si>
     <t xml:space="preserve">Станок с прибором упаковал ____________________Ковылин А.А           «_____» ___________ 2026г</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Лист замечаний</t>
   </si>
 </sst>
 </file>
@@ -349,7 +353,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -496,6 +500,10 @@
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1432,4 +1440,89 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="C2:F52"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="6.49"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C2" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="B3:G52"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;KffffffСтраница &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/1.xlsx
+++ b/1.xlsx
@@ -502,8 +502,8 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1447,22 +1447,25 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="C2:F52"/>
+  <dimension ref="B1:F52"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="6.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="15" width="5.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="6.49"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C2" s="37" t="s">
+      <c r="C2" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="37"/>
+    </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -1513,9 +1516,8 @@
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="C2:F2"/>
-    <mergeCell ref="B3:G52"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
